--- a/artfynd/A 5924-2026 artfynd.xlsx
+++ b/artfynd/A 5924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112704584</v>
+        <v>113001314</v>
       </c>
       <c r="B2" t="n">
-        <v>95985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>825715</v>
+        <v>825515</v>
       </c>
       <c r="R2" t="n">
-        <v>7295702</v>
+        <v>7295797</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112704572</v>
+        <v>113590349</v>
       </c>
       <c r="B3" t="n">
-        <v>56657</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,46 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Notviken, Nb</t>
+          <t>Naturen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>825945</v>
+        <v>825572</v>
       </c>
       <c r="R3" t="n">
-        <v>7295575</v>
+        <v>7295769</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -864,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Från öst</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113001153</v>
+        <v>113590348</v>
       </c>
       <c r="B4" t="n">
-        <v>89975</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,40 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Notviken, Nb</t>
+          <t>Naturen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>825567</v>
+        <v>825572</v>
       </c>
       <c r="R4" t="n">
-        <v>7295770</v>
+        <v>7295768</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,42 +970,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113001155</v>
+        <v>112704572</v>
       </c>
       <c r="B5" t="n">
-        <v>90025</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,13 +1017,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>825567</v>
+        <v>825945</v>
       </c>
       <c r="R5" t="n">
-        <v>7295770</v>
+        <v>7295575</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,12 +1047,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Från öst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,7 +1066,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1113,53 +1084,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113590349</v>
+        <v>113001316</v>
       </c>
       <c r="B6" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naturen, Nb</t>
+          <t>Notviken, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>825572</v>
+        <v>825515</v>
       </c>
       <c r="R6" t="n">
-        <v>7295769</v>
+        <v>7295797</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,12 +1192,7 @@
         <v>113590780</v>
       </c>
       <c r="B7" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,108 +1283,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>113590348</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Naturen, Nb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>825572</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7295768</v>
-      </c>
-      <c r="S8" t="n">
-        <v>50</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Luleå</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Sofia Hagsand</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Sofia Hagsand</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5924-2026 artfynd.xlsx
+++ b/artfynd/A 5924-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001314</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113590349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113590348</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112704572</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113001316</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,8 +1313,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113590780</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>